--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
